--- a/语文群_20261008.xlsx
+++ b/语文群_20261008.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qingg\Python\checkin\WeChatTextExport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_FE6A51EBC8D6971EBB3437C4119344C1EE58E6C6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_FE6A51EB99EE11073B34377EC99470DBEE58E6C6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,7 +427,7 @@
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B1">
         <f>SUM(B3:B10000)</f>
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -885,10 +885,10 @@
       </c>
       <c r="B32" s="2">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" s="2">
         <v>7</v>
